--- a/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAVIER</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -695,7 +713,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -725,6 +743,52 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920005</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920093</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,37 @@
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ALAMILLO</t>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
   </si>
   <si>
     <t>CRISTIAN JAVIER</t>
   </si>
   <si>
-    <t>JOHAN ALEJANDRO</t>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -486,7 +504,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -495,10 +513,10 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>87.18000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -577,19 +595,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -603,16 +624,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -662,22 +686,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>87.18000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -694,13 +718,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>57.69</v>
+        <v>61.54</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -713,7 +737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -751,10 +775,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -768,25 +792,71 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920093</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920393</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920073</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
     <t>MIXCOHA</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>CANUTO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>EVARISTO</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
   </si>
   <si>
     <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -737,7 +728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -769,16 +760,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -792,16 +783,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920089</v>
+        <v>21330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -815,48 +806,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920393</v>
+        <v>20330051920073</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920073</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -76,25 +76,16 @@
     <t>MIXCOHA</t>
   </si>
   <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>CANUTO</t>
   </si>
   <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>MEDINA</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
   </si>
   <si>
     <t>ISRAEL</t>
@@ -589,16 +580,16 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -728,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -766,10 +757,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -783,47 +774,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920393</v>
+        <v>20330051920073</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920073</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,70 @@
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>URBINA</t>
+  </si>
+  <si>
     <t>CANUTO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -674,16 +725,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>82.5</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +751,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>61.54</v>
+        <v>42.31</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +770,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -757,10 +808,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -774,25 +825,186 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920073</v>
+        <v>21330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920073</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920051</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920080</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920082</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920070</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920195</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920081</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -134,6 +140,9 @@
   </si>
   <si>
     <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
   </si>
   <si>
     <t>OSVALDO</t>
@@ -770,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -808,10 +817,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -831,10 +840,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -854,10 +863,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -877,10 +886,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -900,10 +909,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -923,10 +932,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -940,16 +949,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920070</v>
+        <v>20330051920091</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -963,39 +972,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920195</v>
+        <v>20330051920070</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920081</v>
+        <v>21330051920195</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1004,6 +1013,29 @@
         <v>10</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920081</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>
